--- a/excel/dialogue.xlsx
+++ b/excel/dialogue.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="7895" windowHeight="4452"/>
+    <workbookView windowWidth="30720" windowHeight="13500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,28 +28,274 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+文本变体</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="53">
   <si>
     <t>id</t>
   </si>
   <si>
+    <t>speaker</t>
+  </si>
+  <si>
     <t>text</t>
+  </si>
+  <si>
+    <t>text_variants</t>
+  </si>
+  <si>
+    <t>options</t>
+  </si>
+  <si>
+    <t>options_resoult</t>
+  </si>
+  <si>
+    <t>next</t>
+  </si>
+  <si>
+    <t>effects</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>waitTime</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>interval</t>
+  </si>
+  <si>
+    <t>键</t>
+  </si>
+  <si>
+    <t>对象</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>内容变体，二次和三次聊天（文本变体）填写对话id /或者以后改成直接变体，不用判断(或者算是分支)
+只能是顺序数组
+没有就空着不要填写</t>
+  </si>
+  <si>
+    <t>选项，或者其他信息可以用这样包装[{1:"",2:"",3:""}] 内容指向下一个对话</t>
+  </si>
+  <si>
+    <t>每个选择对应的结果</t>
+  </si>
+  <si>
+    <t>稳定下一步，可以多个下一步，每个分别做条件判断,【不用选择的默认下一步】</t>
+  </si>
+  <si>
+    <t>效果提示</t>
+  </si>
+  <si>
+    <t>出现条件判断
+manual -条件判断，value写代码
+weight -权重，value填写数字
+auto -没条件
+state{playerIsIn,time,}</t>
+  </si>
+  <si>
+    <t>&gt;0是自动结束
+=-1是点击结束
+=-2是音乐结束就结束</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">是否中途话题
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>plot-剧情
+topic-话题
+action-动作</t>
+    </r>
+  </si>
+  <si>
+    <t>冷却期，多久不能进入
+/分钟</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>nian</t>
+  </si>
+  <si>
+    <t>初次见面!</t>
+  </si>
+  <si>
+    <t>["first2","greeting"]</t>
+  </si>
+  <si>
+    <t>["secend"]</t>
+  </si>
+  <si>
+    <t>plot</t>
+  </si>
+  <si>
+    <t>greeting</t>
+  </si>
+  <si>
+    <t>hello!</t>
+  </si>
+  <si>
+    <t>{"type":"weight","value":"3"}</t>
+  </si>
+  <si>
+    <t>secend</t>
+  </si>
+  <si>
+    <t>拖入音乐文件就可以听歌了哦</t>
+  </si>
+  <si>
+    <t>first2</t>
+  </si>
+  <si>
+    <t>hi，又见面了呀！</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>现在时间{{time}}</t>
+  </si>
+  <si>
+    <t>{"type":"manual","value":"time&lt;7:00"}</t>
+  </si>
+  <si>
+    <t>topicTest</t>
+  </si>
+  <si>
+    <t>:3</t>
+  </si>
+  <si>
+    <t>["xvx","ovo",":3"]</t>
+  </si>
+  <si>
+    <t>topic</t>
+  </si>
+  <si>
+    <t>xvx</t>
+  </si>
+  <si>
+    <t>ovo</t>
+  </si>
+  <si>
+    <t>hello</t>
+  </si>
+  <si>
+    <t>["hello2"]</t>
+  </si>
+  <si>
+    <t>hello2</t>
+  </si>
+  <si>
+    <t>有没有兴趣来听下一首</t>
+  </si>
+  <si>
+    <t>["hello3"]</t>
+  </si>
+  <si>
+    <t>hello3</t>
+  </si>
+  <si>
+    <t>我也很感兴趣呢</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -199,8 +445,19 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -209,6 +466,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -394,12 +663,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -520,76 +804,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
@@ -598,10 +876,10 @@
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
@@ -610,10 +888,10 @@
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
@@ -622,10 +900,10 @@
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
@@ -634,10 +912,10 @@
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
@@ -646,13 +924,37 @@
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -965,29 +1267,396 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1"/>
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="22.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="25.6666666666667" customWidth="1"/>
+    <col min="5" max="5" width="42.6666666666667" customWidth="1"/>
+    <col min="6" max="7" width="27.5555555555556" customWidth="1"/>
+    <col min="8" max="8" width="11.7777777777778" customWidth="1"/>
+    <col min="9" max="9" width="34.8888888888889" customWidth="1"/>
+    <col min="11" max="11" width="16.5555555555556" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
+    <row r="2" ht="100.8" spans="1:16">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>22</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" t="s">
+        <v>47</v>
+      </c>
+      <c r="I12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12">
+        <v>-1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:16">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13">
+        <v>-1</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14">
+        <v>-1</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
